--- a/BOQ_AlWaha_C1.xlsx
+++ b/BOQ_AlWaha_C1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My-CODE_RUSH\projects\Quantity Savior\client\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D625F43E-656D-443A-BA1F-93CD17A13DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74DFD67-3D73-4C55-80D4-39966189422E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="349">
   <si>
     <t>BILL OF QUANTITIES  ·  KITCHEN FITOUT  ·  TYPE C01</t>
   </si>
@@ -409,7 +409,7 @@
     <t>A18</t>
   </si>
   <si>
-    <t>Total lipping per unit: 3.78 lm</t>
+    <t>Total per unit: 3.78 lm</t>
   </si>
   <si>
     <t>Side Panel</t>
@@ -868,10 +868,20 @@
     <t>Total per unit: 1.15 lm</t>
   </si>
   <si>
-    <t xml:space="preserve">  FIXTURES  </t>
-  </si>
-  <si>
-    <t>KITCHEN FIXTURES</t>
+    <t xml:space="preserve">  FX  </t>
+  </si>
+  <si>
+    <t>KITCHEN FIXTURES – INSTALLED ITEMS SCHEDULE</t>
+  </si>
+  <si>
+    <t>Qty / Unit</t>
+  </si>
+  <si>
+    <t>Total Qty
+(Project)</t>
+  </si>
+  <si>
+    <t>— MATERIAL SCOPE N/A  ·  Installed Fixtures Only —</t>
   </si>
   <si>
     <t>F1</t>
@@ -940,7 +950,7 @@
     <t>AL WAHA RESIDENCE 01   ·   EXPO CITY DUBAI   ·   TYPE C01   ·   58 Units</t>
   </si>
   <si>
-    <t>★  All quantities are live-linked from BOQ_Matrix row 158. Edit dimensions in BOQ_Matrix; this sheet updates automatically.</t>
+    <t>★  All quantities are live-linked from BOQ_Matrix row 157. Edit dimensions in BOQ_Matrix; this sheet updates automatically.</t>
   </si>
   <si>
     <t>#</t>
@@ -970,6 +980,9 @@
     <t>6mm Both-Face Melamine MR MDF Sheet</t>
   </si>
   <si>
+    <t>Per m² supplied</t>
+  </si>
+  <si>
     <t>9mm_mdf</t>
   </si>
   <si>
@@ -1006,6 +1019,9 @@
     <t>PL-01 Laminate (0.8mm)</t>
   </si>
   <si>
+    <t>Per m² supplied &amp; bonded</t>
+  </si>
+  <si>
     <t>hinges</t>
   </si>
   <si>
@@ -1015,19 +1031,34 @@
     <t>Nr / Pr</t>
   </si>
   <si>
+    <t>Per hinge supplied &amp; fixed</t>
+  </si>
+  <si>
     <t>drawer_runners</t>
   </si>
   <si>
     <t>Drawer Runner (0.5m)</t>
   </si>
   <si>
+    <t>Per pair supplied &amp; fixed</t>
+  </si>
+  <si>
     <t>pvc_lipping_25mm</t>
   </si>
   <si>
+    <t>Per LM supplied &amp; glued</t>
+  </si>
+  <si>
     <t>pvc_lipping_18mm</t>
   </si>
   <si>
-    <t>Sheet size basis: 2.88 m² per board  ·  Sheets Needed column rounds UP to whole boards  ·  Count/Linear/Volume items show actual quantities.</t>
+    <t>INSTALLED FIXTURES  ·  SCHEDULE OF QUANTITIES</t>
+  </si>
+  <si>
+    <t>Item No</t>
+  </si>
+  <si>
+    <t>Sheet size basis: 2.88 m² per board  ·  Sheets Needed rounds UP to whole boards  ·  Count/Linear/Volume items show actual quantities.</t>
   </si>
   <si>
     <t>COST BREAKDOWN  ·  MATERIAL QUANTITIES × UNIT RATES</t>
@@ -1036,7 +1067,7 @@
     <t>AL WAHA RESIDENCE 01   ·   EXPO CITY DUBAI   ·   TYPE C01   ·   58 Units   ·   Currency: AED   ·   VAT: 5%</t>
   </si>
   <si>
-    <t>★  Enter unit rates in column G (AED/unit). Amount = Total Qty × Unit Rate. Totals update automatically.</t>
+    <t>★  Unit rates in column G are pre-filled where cost data exists in the source JSON. Amber cells = contractor to fill. Green cells = rate from data. Amount = Total Qty × Unit Rate.</t>
   </si>
   <si>
     <t>Total Qty</t>
@@ -1051,6 +1082,9 @@
   </si>
   <si>
     <t>Notes</t>
+  </si>
+  <si>
+    <t>INSTALLED FIXTURES  ·  SUPPLY &amp; INSTALLATION RATES</t>
   </si>
   <si>
     <t>SUBTOTAL  (excl. VAT)</t>
@@ -1256,6 +1290,20 @@
       <family val="2"/>
     </font>
     <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF6C7A8D"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
@@ -1270,13 +1318,6 @@
       <family val="2"/>
     </font>
     <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF6C7A8D"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF1A5C3A"/>
@@ -1286,12 +1327,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF6C7A8D"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0D1B2A"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1317,7 +1352,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1394,8 +1429,28 @@
         <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF5FB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F2F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F4F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6F0E0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1607,6 +1662,119 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FFB8962E"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFB8962E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFC8A84B"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFC8A84B"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFB8962E"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFB8962E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE8EDF5"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8EDF5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8EDF5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8EDF5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE0C060"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFE8EDF5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8EDF5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFE8EDF5"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8EDF5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE8EDF5"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDDE3EE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDDE3EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDE3EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDE3EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDE3EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDE3EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDE3EE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDE3EE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDE3EE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFDDEEFF"/>
       </left>
@@ -1655,7 +1823,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1809,28 +1977,60 @@
     <xf numFmtId="164" fontId="25" fillId="15" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="19" fillId="10" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="19" fillId="10" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1841,22 +2041,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="13" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="13" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1865,50 +2065,62 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="10" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="31" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="13" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="13" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="15" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="15" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="32" fillId="13" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="31" fillId="10" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="6" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="10" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="31" fillId="19" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="15" fillId="6" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="34" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="34" fillId="4" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="35" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="35" fillId="3" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1932,25 +2144,48 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2275,22 +2510,22 @@
     </row>
     <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
-      <c r="B2" s="108" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="109"/>
-      <c r="D2" s="109"/>
-      <c r="E2" s="109"/>
+      <c r="B2" s="124" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="106" t="s">
+      <c r="B3" s="122" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
       <c r="F3" s="4"/>
     </row>
     <row r="4" spans="1:6" ht="3" customHeight="1" x14ac:dyDescent="0.3">
@@ -2303,12 +2538,12 @@
     </row>
     <row r="5" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5"/>
-      <c r="B5" s="104" t="s">
+      <c r="B5" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
       <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2316,11 +2551,11 @@
       <c r="B6" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="101" t="s">
+      <c r="C6" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2328,11 +2563,11 @@
       <c r="B7" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="103" t="s">
+      <c r="C7" s="119" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
       <c r="F7" s="12"/>
     </row>
     <row r="8" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2340,11 +2575,11 @@
       <c r="B8" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="101" t="s">
+      <c r="C8" s="117" t="s">
         <v>8</v>
       </c>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2352,11 +2587,11 @@
       <c r="B9" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="103" t="s">
+      <c r="C9" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
       <c r="F9" s="12"/>
     </row>
     <row r="10" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2364,11 +2599,11 @@
       <c r="B10" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="101">
+      <c r="C10" s="117">
         <v>58</v>
       </c>
-      <c r="D10" s="102"/>
-      <c r="E10" s="102"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2376,11 +2611,11 @@
       <c r="B11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="103" t="s">
+      <c r="C11" s="119" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
       <c r="F11" s="12"/>
     </row>
     <row r="12" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2388,11 +2623,11 @@
       <c r="B12" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="101" t="s">
+      <c r="C12" s="117" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2400,22 +2635,22 @@
       <c r="B13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="103" t="s">
+      <c r="C13" s="119" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
       <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="15" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
-      <c r="B15" s="104" t="s">
+      <c r="B15" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="105"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="105"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="121"/>
+      <c r="E15" s="121"/>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2423,11 +2658,11 @@
       <c r="B16" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="101" t="s">
+      <c r="C16" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="102"/>
-      <c r="E16" s="102"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2435,11 +2670,11 @@
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="103" t="s">
+      <c r="C17" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="102"/>
-      <c r="E17" s="102"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
       <c r="F17" s="12"/>
     </row>
     <row r="18" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2447,11 +2682,11 @@
       <c r="B18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="101" t="s">
+      <c r="C18" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="102"/>
-      <c r="E18" s="102"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2459,22 +2694,22 @@
       <c r="B19" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="103" t="s">
+      <c r="C19" s="119" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="102"/>
-      <c r="E19" s="102"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
       <c r="F19" s="12"/>
     </row>
     <row r="20" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="21" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="5"/>
-      <c r="B21" s="104" t="s">
+      <c r="B21" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="105"/>
-      <c r="D21" s="105"/>
-      <c r="E21" s="105"/>
+      <c r="C21" s="121"/>
+      <c r="D21" s="121"/>
+      <c r="E21" s="121"/>
       <c r="F21" s="6"/>
     </row>
     <row r="22" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2576,12 +2811,12 @@
     <row r="28" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="5"/>
-      <c r="B29" s="104" t="s">
+      <c r="B29" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="C29" s="105"/>
-      <c r="D29" s="105"/>
-      <c r="E29" s="105"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
       <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2589,11 +2824,11 @@
       <c r="B30" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C30" s="101" t="s">
+      <c r="C30" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D30" s="102"/>
-      <c r="E30" s="102"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2601,11 +2836,11 @@
       <c r="B31" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C31" s="103" t="s">
+      <c r="C31" s="119" t="s">
         <v>42</v>
       </c>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
       <c r="F31" s="12"/>
     </row>
     <row r="32" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2613,11 +2848,11 @@
       <c r="B32" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="101" t="s">
+      <c r="C32" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="102"/>
-      <c r="E32" s="102"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
       <c r="F32" s="9"/>
     </row>
     <row r="33" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2625,11 +2860,11 @@
       <c r="B33" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="103" t="s">
+      <c r="C33" s="119" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="102"/>
-      <c r="E33" s="102"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
       <c r="F33" s="12"/>
     </row>
     <row r="34" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2637,22 +2872,22 @@
       <c r="B34" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C34" s="101" t="s">
+      <c r="C34" s="117" t="s">
         <v>48</v>
       </c>
-      <c r="D34" s="102"/>
-      <c r="E34" s="102"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="1:6" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="5"/>
-      <c r="B36" s="104" t="s">
+      <c r="B36" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="105"/>
-      <c r="D36" s="105"/>
-      <c r="E36" s="105"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="121"/>
+      <c r="E36" s="121"/>
       <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2660,11 +2895,11 @@
       <c r="B37" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="101" t="s">
+      <c r="C37" s="117" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="102"/>
-      <c r="E37" s="102"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
       <c r="F37" s="9"/>
     </row>
     <row r="38" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2672,11 +2907,11 @@
       <c r="B38" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="103" t="s">
+      <c r="C38" s="119" t="s">
         <v>53</v>
       </c>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
       <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2684,11 +2919,11 @@
       <c r="B39" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="101" t="s">
+      <c r="C39" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="D39" s="102"/>
-      <c r="E39" s="102"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -2696,11 +2931,11 @@
       <c r="B40" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="103" t="s">
+      <c r="C40" s="119" t="s">
         <v>57</v>
       </c>
-      <c r="D40" s="102"/>
-      <c r="E40" s="102"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
       <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2713,14 +2948,14 @@
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="107" t="s">
+      <c r="A43" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="B43" s="102"/>
-      <c r="C43" s="102"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="102"/>
-      <c r="F43" s="102"/>
+      <c r="B43" s="118"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="118"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -2760,7 +2995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z169"/>
+  <dimension ref="A1:Z168"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -2781,32 +3016,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="137" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="102"/>
-      <c r="C1" s="102"/>
-      <c r="D1" s="102"/>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="102"/>
-      <c r="P1" s="102"/>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="102"/>
-      <c r="S1" s="102"/>
-      <c r="T1" s="102"/>
-      <c r="U1" s="102"/>
-      <c r="V1" s="102"/>
-      <c r="W1" s="102"/>
-      <c r="X1" s="102"/>
+      <c r="B1" s="118"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="118"/>
+      <c r="K1" s="118"/>
+      <c r="L1" s="118"/>
+      <c r="M1" s="118"/>
+      <c r="N1" s="118"/>
+      <c r="O1" s="118"/>
+      <c r="P1" s="118"/>
+      <c r="Q1" s="118"/>
+      <c r="R1" s="118"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="118"/>
       <c r="Y1" s="24"/>
       <c r="Z1" s="24"/>
     </row>
@@ -8829,552 +9064,508 @@
       <c r="Y144" s="24"/>
       <c r="Z144" s="24"/>
     </row>
-    <row r="145" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="31"/>
-      <c r="B145" s="31" t="s">
+    <row r="145" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="13"/>
+      <c r="B145" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="C145" s="31" t="s">
+      <c r="C145" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="31" t="s">
+      <c r="D145" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="E145" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="F145" s="31" t="s">
-        <v>66</v>
-      </c>
-      <c r="G145" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="H145" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="I145" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="J145" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="K145" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="L145" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="M145" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="N145" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="O145" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="P145" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q145" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="R145" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="S145" s="31" t="s">
-        <v>79</v>
-      </c>
-      <c r="T145" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="U145" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="V145" s="32"/>
-      <c r="W145" s="32"/>
-      <c r="X145" s="31" t="s">
+      <c r="E145" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="F145" s="68"/>
+      <c r="G145" s="68"/>
+      <c r="H145" s="68"/>
+      <c r="I145" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="J145" s="126" t="s">
+        <v>278</v>
+      </c>
+      <c r="K145" s="127"/>
+      <c r="L145" s="127"/>
+      <c r="M145" s="127"/>
+      <c r="N145" s="127"/>
+      <c r="O145" s="127"/>
+      <c r="P145" s="127"/>
+      <c r="Q145" s="127"/>
+      <c r="R145" s="127"/>
+      <c r="S145" s="127"/>
+      <c r="T145" s="127"/>
+      <c r="U145" s="127"/>
+      <c r="V145" s="127"/>
+      <c r="W145" s="127"/>
+      <c r="X145" s="69" t="s">
         <v>82</v>
       </c>
       <c r="Y145" s="24"/>
       <c r="Z145" s="24"/>
     </row>
-    <row r="146" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B146" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="C146" s="65" t="s">
-        <v>277</v>
-      </c>
-      <c r="D146" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="E146" s="66">
+    <row r="146" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="70"/>
+      <c r="B146" s="71" t="s">
+        <v>279</v>
+      </c>
+      <c r="C146" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="D146" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="E146" s="74">
         <v>1</v>
       </c>
-      <c r="I146" s="67">
-        <v>1</v>
-      </c>
-      <c r="J146" s="39"/>
-      <c r="K146" s="39"/>
-      <c r="L146" s="39"/>
-      <c r="M146" s="39"/>
-      <c r="N146" s="39"/>
-      <c r="O146" s="39"/>
-      <c r="P146" s="39"/>
-      <c r="Q146" s="39"/>
-      <c r="R146" s="39"/>
-      <c r="S146" s="39"/>
-      <c r="T146" s="39"/>
-      <c r="U146" s="39"/>
-      <c r="X146" s="45" t="s">
-        <v>279</v>
+      <c r="F146" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="G146" s="133"/>
+      <c r="H146" s="134"/>
+      <c r="I146" s="75">
+        <f>E146*H2</f>
+        <v>58</v>
+      </c>
+      <c r="J146" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="K146" s="133"/>
+      <c r="L146" s="133"/>
+      <c r="M146" s="133"/>
+      <c r="N146" s="133"/>
+      <c r="O146" s="133"/>
+      <c r="P146" s="133"/>
+      <c r="Q146" s="133"/>
+      <c r="R146" s="133"/>
+      <c r="S146" s="133"/>
+      <c r="T146" s="133"/>
+      <c r="U146" s="133"/>
+      <c r="V146" s="133"/>
+      <c r="W146" s="134"/>
+      <c r="X146" s="76" t="s">
+        <v>282</v>
       </c>
       <c r="Y146" s="24"/>
       <c r="Z146" s="24"/>
     </row>
-    <row r="147" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B147" s="46" t="s">
-        <v>280</v>
-      </c>
-      <c r="C147" s="68" t="s">
+    <row r="147" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="70"/>
+      <c r="B147" s="77" t="s">
+        <v>283</v>
+      </c>
+      <c r="C147" s="78" t="s">
+        <v>284</v>
+      </c>
+      <c r="D147" s="79" t="s">
         <v>281</v>
       </c>
-      <c r="D147" s="48" t="s">
-        <v>278</v>
-      </c>
-      <c r="E147" s="69">
+      <c r="E147" s="80">
         <v>1</v>
       </c>
-      <c r="I147" s="70">
-        <v>1</v>
-      </c>
-      <c r="J147" s="49"/>
-      <c r="K147" s="49"/>
-      <c r="L147" s="49"/>
-      <c r="M147" s="49"/>
-      <c r="N147" s="49"/>
-      <c r="O147" s="49"/>
-      <c r="P147" s="49"/>
-      <c r="Q147" s="49"/>
-      <c r="R147" s="49"/>
-      <c r="S147" s="49"/>
-      <c r="T147" s="49"/>
-      <c r="U147" s="49"/>
-      <c r="X147" s="55" t="s">
-        <v>282</v>
+      <c r="F147" s="128" t="s">
+        <v>102</v>
+      </c>
+      <c r="G147" s="129"/>
+      <c r="H147" s="130"/>
+      <c r="I147" s="81">
+        <f>E147*H2</f>
+        <v>58</v>
+      </c>
+      <c r="J147" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="K147" s="129"/>
+      <c r="L147" s="129"/>
+      <c r="M147" s="129"/>
+      <c r="N147" s="129"/>
+      <c r="O147" s="129"/>
+      <c r="P147" s="129"/>
+      <c r="Q147" s="129"/>
+      <c r="R147" s="129"/>
+      <c r="S147" s="129"/>
+      <c r="T147" s="129"/>
+      <c r="U147" s="129"/>
+      <c r="V147" s="129"/>
+      <c r="W147" s="130"/>
+      <c r="X147" s="82" t="s">
+        <v>285</v>
       </c>
       <c r="Y147" s="24"/>
       <c r="Z147" s="24"/>
     </row>
-    <row r="148" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B148" s="36" t="s">
-        <v>283</v>
-      </c>
-      <c r="C148" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="D148" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="E148" s="66">
+    <row r="148" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="70"/>
+      <c r="B148" s="71" t="s">
+        <v>286</v>
+      </c>
+      <c r="C148" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="D148" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="E148" s="74">
         <v>1</v>
       </c>
-      <c r="I148" s="67">
-        <v>1</v>
-      </c>
-      <c r="J148" s="39"/>
-      <c r="K148" s="39"/>
-      <c r="L148" s="39"/>
-      <c r="M148" s="39"/>
-      <c r="N148" s="39"/>
-      <c r="O148" s="39"/>
-      <c r="P148" s="39"/>
-      <c r="Q148" s="39"/>
-      <c r="R148" s="39"/>
-      <c r="S148" s="39"/>
-      <c r="T148" s="39"/>
-      <c r="U148" s="39"/>
-      <c r="X148" s="45" t="s">
-        <v>285</v>
+      <c r="F148" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="G148" s="133"/>
+      <c r="H148" s="134"/>
+      <c r="I148" s="75">
+        <f>E148*H2</f>
+        <v>58</v>
+      </c>
+      <c r="J148" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="K148" s="133"/>
+      <c r="L148" s="133"/>
+      <c r="M148" s="133"/>
+      <c r="N148" s="133"/>
+      <c r="O148" s="133"/>
+      <c r="P148" s="133"/>
+      <c r="Q148" s="133"/>
+      <c r="R148" s="133"/>
+      <c r="S148" s="133"/>
+      <c r="T148" s="133"/>
+      <c r="U148" s="133"/>
+      <c r="V148" s="133"/>
+      <c r="W148" s="134"/>
+      <c r="X148" s="76" t="s">
+        <v>288</v>
       </c>
       <c r="Y148" s="24"/>
       <c r="Z148" s="24"/>
     </row>
-    <row r="149" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B149" s="46" t="s">
-        <v>286</v>
-      </c>
-      <c r="C149" s="68" t="s">
-        <v>287</v>
-      </c>
-      <c r="D149" s="48" t="s">
-        <v>278</v>
-      </c>
-      <c r="E149" s="69">
+    <row r="149" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A149" s="70"/>
+      <c r="B149" s="77" t="s">
+        <v>289</v>
+      </c>
+      <c r="C149" s="78" t="s">
+        <v>290</v>
+      </c>
+      <c r="D149" s="79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E149" s="80">
         <v>1</v>
       </c>
-      <c r="I149" s="70">
-        <v>1</v>
-      </c>
-      <c r="J149" s="49"/>
-      <c r="K149" s="49"/>
-      <c r="L149" s="49"/>
-      <c r="M149" s="49"/>
-      <c r="N149" s="49"/>
-      <c r="O149" s="49"/>
-      <c r="P149" s="49"/>
-      <c r="Q149" s="49"/>
-      <c r="R149" s="49"/>
-      <c r="S149" s="49"/>
-      <c r="T149" s="49"/>
-      <c r="U149" s="49"/>
-      <c r="X149" s="55" t="s">
-        <v>288</v>
+      <c r="F149" s="128" t="s">
+        <v>102</v>
+      </c>
+      <c r="G149" s="129"/>
+      <c r="H149" s="130"/>
+      <c r="I149" s="81">
+        <f>E149*H2</f>
+        <v>58</v>
+      </c>
+      <c r="J149" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="K149" s="129"/>
+      <c r="L149" s="129"/>
+      <c r="M149" s="129"/>
+      <c r="N149" s="129"/>
+      <c r="O149" s="129"/>
+      <c r="P149" s="129"/>
+      <c r="Q149" s="129"/>
+      <c r="R149" s="129"/>
+      <c r="S149" s="129"/>
+      <c r="T149" s="129"/>
+      <c r="U149" s="129"/>
+      <c r="V149" s="129"/>
+      <c r="W149" s="130"/>
+      <c r="X149" s="82" t="s">
+        <v>291</v>
       </c>
       <c r="Y149" s="24"/>
       <c r="Z149" s="24"/>
     </row>
-    <row r="150" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B150" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="C150" s="65" t="s">
-        <v>290</v>
-      </c>
-      <c r="D150" s="38" t="s">
-        <v>278</v>
-      </c>
-      <c r="E150" s="66">
+    <row r="150" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="70"/>
+      <c r="B150" s="71" t="s">
+        <v>292</v>
+      </c>
+      <c r="C150" s="72" t="s">
+        <v>293</v>
+      </c>
+      <c r="D150" s="73" t="s">
+        <v>281</v>
+      </c>
+      <c r="E150" s="74">
         <v>1</v>
       </c>
-      <c r="I150" s="67">
-        <v>1</v>
-      </c>
-      <c r="J150" s="39"/>
-      <c r="K150" s="39"/>
-      <c r="L150" s="39"/>
-      <c r="M150" s="39"/>
-      <c r="N150" s="39"/>
-      <c r="O150" s="39"/>
-      <c r="P150" s="39"/>
-      <c r="Q150" s="39"/>
-      <c r="R150" s="39"/>
-      <c r="S150" s="39"/>
-      <c r="T150" s="39"/>
-      <c r="U150" s="39"/>
-      <c r="X150" s="45" t="s">
-        <v>291</v>
+      <c r="F150" s="132" t="s">
+        <v>102</v>
+      </c>
+      <c r="G150" s="133"/>
+      <c r="H150" s="134"/>
+      <c r="I150" s="75">
+        <f>E150*H2</f>
+        <v>58</v>
+      </c>
+      <c r="J150" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="K150" s="133"/>
+      <c r="L150" s="133"/>
+      <c r="M150" s="133"/>
+      <c r="N150" s="133"/>
+      <c r="O150" s="133"/>
+      <c r="P150" s="133"/>
+      <c r="Q150" s="133"/>
+      <c r="R150" s="133"/>
+      <c r="S150" s="133"/>
+      <c r="T150" s="133"/>
+      <c r="U150" s="133"/>
+      <c r="V150" s="133"/>
+      <c r="W150" s="134"/>
+      <c r="X150" s="76" t="s">
+        <v>294</v>
       </c>
       <c r="Y150" s="24"/>
       <c r="Z150" s="24"/>
     </row>
-    <row r="151" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B151" s="46" t="s">
-        <v>292</v>
-      </c>
-      <c r="C151" s="68" t="s">
-        <v>293</v>
-      </c>
-      <c r="D151" s="48" t="s">
-        <v>278</v>
-      </c>
-      <c r="E151" s="69">
+    <row r="151" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A151" s="70"/>
+      <c r="B151" s="77" t="s">
+        <v>295</v>
+      </c>
+      <c r="C151" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="D151" s="79" t="s">
+        <v>281</v>
+      </c>
+      <c r="E151" s="80">
         <v>15</v>
       </c>
-      <c r="I151" s="70">
-        <v>15</v>
-      </c>
-      <c r="J151" s="49"/>
-      <c r="K151" s="49"/>
-      <c r="L151" s="49"/>
-      <c r="M151" s="49"/>
-      <c r="N151" s="49"/>
-      <c r="O151" s="49"/>
-      <c r="P151" s="49"/>
-      <c r="Q151" s="49"/>
-      <c r="R151" s="49"/>
-      <c r="S151" s="49"/>
-      <c r="T151" s="49"/>
-      <c r="U151" s="49"/>
-      <c r="X151" s="55" t="s">
-        <v>294</v>
+      <c r="F151" s="128" t="s">
+        <v>102</v>
+      </c>
+      <c r="G151" s="129"/>
+      <c r="H151" s="130"/>
+      <c r="I151" s="81">
+        <f>E151*H2</f>
+        <v>870</v>
+      </c>
+      <c r="J151" s="131" t="s">
+        <v>102</v>
+      </c>
+      <c r="K151" s="129"/>
+      <c r="L151" s="129"/>
+      <c r="M151" s="129"/>
+      <c r="N151" s="129"/>
+      <c r="O151" s="129"/>
+      <c r="P151" s="129"/>
+      <c r="Q151" s="129"/>
+      <c r="R151" s="129"/>
+      <c r="S151" s="129"/>
+      <c r="T151" s="129"/>
+      <c r="U151" s="129"/>
+      <c r="V151" s="129"/>
+      <c r="W151" s="130"/>
+      <c r="X151" s="82" t="s">
+        <v>297</v>
       </c>
       <c r="Y151" s="24"/>
       <c r="Z151" s="24"/>
     </row>
-    <row r="152" spans="1:26" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I152" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="J152" s="61">
-        <f t="shared" ref="J152:U152" si="5">SUM(J146:J151)</f>
-        <v>0</v>
-      </c>
-      <c r="K152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="N152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="P152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="Q152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="R152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="S152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="T152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="U152" s="61">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+    <row r="152" spans="1:26" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y152" s="24"/>
       <c r="Z152" s="24"/>
     </row>
-    <row r="153" spans="1:26" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="H153" s="62">
-        <f>H2</f>
-        <v>58</v>
-      </c>
-      <c r="I153" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="J153" s="64">
-        <f>J152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="K153" s="64">
-        <f>K152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="L153" s="64">
-        <f>L152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="M153" s="64">
-        <f>M152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="N153" s="64">
-        <f>N152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="O153" s="64">
-        <f>O152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="P153" s="64">
-        <f>P152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="Q153" s="64">
-        <f>Q152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="R153" s="64">
-        <f>R152*H2</f>
-        <v>0</v>
-      </c>
-      <c r="S153" s="64">
-        <f>S152*H2</f>
-        <v>0</v>
-      </c>
-      <c r="T153" s="64">
-        <f>T152*H2/2.88</f>
-        <v>0</v>
-      </c>
-      <c r="U153" s="64">
-        <f>U152*H2/2.88</f>
-        <v>0</v>
-      </c>
+    <row r="153" spans="1:26" x14ac:dyDescent="0.3">
       <c r="Y153" s="24"/>
       <c r="Z153" s="24"/>
     </row>
-    <row r="154" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="Y154" s="24"/>
       <c r="Z154" s="24"/>
     </row>
-    <row r="155" spans="1:26" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A155" s="1"/>
+      <c r="B155" s="1"/>
+      <c r="C155" s="1"/>
+      <c r="D155" s="1"/>
+      <c r="E155" s="1"/>
+      <c r="F155" s="1"/>
+      <c r="G155" s="1"/>
+      <c r="H155" s="1"/>
+      <c r="I155" s="1"/>
+      <c r="J155" s="1"/>
+      <c r="K155" s="1"/>
+      <c r="L155" s="1"/>
+      <c r="M155" s="1"/>
+      <c r="N155" s="1"/>
+      <c r="O155" s="1"/>
+      <c r="P155" s="1"/>
+      <c r="Q155" s="1"/>
+      <c r="R155" s="1"/>
+      <c r="S155" s="1"/>
+      <c r="T155" s="1"/>
+      <c r="U155" s="1"/>
+      <c r="V155" s="1"/>
+      <c r="W155" s="1"/>
+      <c r="X155" s="1"/>
       <c r="Y155" s="24"/>
       <c r="Z155" s="24"/>
     </row>
-    <row r="156" spans="1:26" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
-      <c r="C156" s="1"/>
-      <c r="D156" s="1"/>
-      <c r="E156" s="1"/>
-      <c r="F156" s="1"/>
-      <c r="G156" s="1"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="1"/>
-      <c r="J156" s="1"/>
-      <c r="K156" s="1"/>
-      <c r="L156" s="1"/>
-      <c r="M156" s="1"/>
-      <c r="N156" s="1"/>
-      <c r="O156" s="1"/>
-      <c r="P156" s="1"/>
-      <c r="Q156" s="1"/>
-      <c r="R156" s="1"/>
-      <c r="S156" s="1"/>
-      <c r="T156" s="1"/>
-      <c r="U156" s="1"/>
-      <c r="V156" s="1"/>
-      <c r="W156" s="1"/>
-      <c r="X156" s="1"/>
+    <row r="156" spans="1:26" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A156" s="136" t="s">
+        <v>298</v>
+      </c>
+      <c r="B156" s="118"/>
+      <c r="C156" s="118"/>
+      <c r="D156" s="118"/>
+      <c r="E156" s="118"/>
+      <c r="F156" s="118"/>
+      <c r="G156" s="118"/>
+      <c r="H156" s="118"/>
+      <c r="I156" s="118"/>
+      <c r="J156" s="118"/>
+      <c r="K156" s="118"/>
+      <c r="L156" s="118"/>
+      <c r="M156" s="118"/>
+      <c r="N156" s="118"/>
+      <c r="O156" s="118"/>
+      <c r="P156" s="118"/>
+      <c r="Q156" s="118"/>
+      <c r="R156" s="118"/>
+      <c r="S156" s="118"/>
+      <c r="T156" s="118"/>
+      <c r="U156" s="118"/>
+      <c r="V156" s="118"/>
+      <c r="W156" s="118"/>
+      <c r="X156" s="118"/>
       <c r="Y156" s="24"/>
       <c r="Z156" s="24"/>
     </row>
-    <row r="157" spans="1:26" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="110" t="s">
-        <v>295</v>
-      </c>
-      <c r="B157" s="102"/>
-      <c r="C157" s="102"/>
-      <c r="D157" s="102"/>
-      <c r="E157" s="102"/>
-      <c r="F157" s="102"/>
-      <c r="G157" s="102"/>
-      <c r="H157" s="102"/>
-      <c r="I157" s="102"/>
-      <c r="J157" s="102"/>
-      <c r="K157" s="102"/>
-      <c r="L157" s="102"/>
-      <c r="M157" s="102"/>
-      <c r="N157" s="102"/>
-      <c r="O157" s="102"/>
-      <c r="P157" s="102"/>
-      <c r="Q157" s="102"/>
-      <c r="R157" s="102"/>
-      <c r="S157" s="102"/>
-      <c r="T157" s="102"/>
-      <c r="U157" s="102"/>
-      <c r="V157" s="102"/>
-      <c r="W157" s="102"/>
-      <c r="X157" s="102"/>
+    <row r="157" spans="1:26" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I157" s="83" t="s">
+        <v>69</v>
+      </c>
+      <c r="J157" s="84">
+        <f t="shared" ref="J157:U157" si="5">J33+J54+J82+J117+J142</f>
+        <v>17.319444444444443</v>
+      </c>
+      <c r="K157" s="84">
+        <f t="shared" si="5"/>
+        <v>155.19631944444444</v>
+      </c>
+      <c r="L157" s="84">
+        <f t="shared" si="5"/>
+        <v>32.230277777777779</v>
+      </c>
+      <c r="M157" s="84">
+        <f t="shared" si="5"/>
+        <v>685.08069444444459</v>
+      </c>
+      <c r="N157" s="84">
+        <f t="shared" si="5"/>
+        <v>155.19631944444444</v>
+      </c>
+      <c r="O157" s="84">
+        <f t="shared" si="5"/>
+        <v>46.331527777777772</v>
+      </c>
+      <c r="P157" s="84">
+        <f t="shared" si="5"/>
+        <v>54.375</v>
+      </c>
+      <c r="Q157" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="R157" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="S157" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="T157" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="U157" s="84">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="Y157" s="24"/>
       <c r="Z157" s="24"/>
     </row>
-    <row r="158" spans="1:26" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I158" s="71" t="s">
-        <v>69</v>
-      </c>
-      <c r="J158" s="72">
-        <f t="shared" ref="J158:U158" si="6">J33+J54+J82+J117+J142+J153</f>
-        <v>17.319444444444443</v>
-      </c>
-      <c r="K158" s="72">
-        <f t="shared" si="6"/>
-        <v>155.19631944444444</v>
-      </c>
-      <c r="L158" s="72">
-        <f t="shared" si="6"/>
-        <v>32.230277777777779</v>
-      </c>
-      <c r="M158" s="72">
-        <f t="shared" si="6"/>
-        <v>685.08069444444459</v>
-      </c>
-      <c r="N158" s="72">
-        <f t="shared" si="6"/>
-        <v>155.19631944444444</v>
-      </c>
-      <c r="O158" s="72">
-        <f t="shared" si="6"/>
-        <v>46.331527777777772</v>
-      </c>
-      <c r="P158" s="72">
-        <f t="shared" si="6"/>
-        <v>54.375</v>
-      </c>
-      <c r="Q158" s="72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R158" s="72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="S158" s="72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="T158" s="72">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="U158" s="72">
-        <f t="shared" si="6"/>
-        <v>0</v>
+    <row r="158" spans="1:26" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J158" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="K158" s="85" t="s">
+        <v>71</v>
+      </c>
+      <c r="L158" s="85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M158" s="85" t="s">
+        <v>73</v>
+      </c>
+      <c r="N158" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="O158" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="P158" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q158" s="85" t="s">
+        <v>77</v>
+      </c>
+      <c r="R158" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="S158" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="T158" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="U158" s="85" t="s">
+        <v>81</v>
       </c>
       <c r="Y158" s="24"/>
       <c r="Z158" s="24"/>
     </row>
-    <row r="159" spans="1:26" ht="55.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J159" s="73" t="s">
-        <v>70</v>
-      </c>
-      <c r="K159" s="73" t="s">
-        <v>71</v>
-      </c>
-      <c r="L159" s="73" t="s">
-        <v>72</v>
-      </c>
-      <c r="M159" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="N159" s="73" t="s">
-        <v>74</v>
-      </c>
-      <c r="O159" s="73" t="s">
-        <v>75</v>
-      </c>
-      <c r="P159" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q159" s="73" t="s">
-        <v>77</v>
-      </c>
-      <c r="R159" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="S159" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="T159" s="73" t="s">
-        <v>80</v>
-      </c>
-      <c r="U159" s="73" t="s">
-        <v>81</v>
-      </c>
+    <row r="159" spans="1:26" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A159" s="24"/>
+      <c r="B159" s="24"/>
+      <c r="C159" s="24"/>
+      <c r="D159" s="24"/>
+      <c r="E159" s="24"/>
+      <c r="F159" s="24"/>
+      <c r="G159" s="24"/>
+      <c r="H159" s="24"/>
+      <c r="I159" s="24"/>
+      <c r="J159" s="24"/>
+      <c r="K159" s="24"/>
+      <c r="L159" s="24"/>
+      <c r="M159" s="24"/>
+      <c r="N159" s="24"/>
+      <c r="O159" s="24"/>
+      <c r="P159" s="24"/>
+      <c r="Q159" s="24"/>
+      <c r="R159" s="24"/>
+      <c r="S159" s="24"/>
+      <c r="T159" s="24"/>
+      <c r="U159" s="24"/>
+      <c r="V159" s="24"/>
+      <c r="W159" s="24"/>
+      <c r="X159" s="24"/>
       <c r="Y159" s="24"/>
       <c r="Z159" s="24"/>
     </row>
@@ -9630,38 +9821,23 @@
       <c r="Y168" s="24"/>
       <c r="Z168" s="24"/>
     </row>
-    <row r="169" spans="1:26" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="24"/>
-      <c r="B169" s="24"/>
-      <c r="C169" s="24"/>
-      <c r="D169" s="24"/>
-      <c r="E169" s="24"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="24"/>
-      <c r="H169" s="24"/>
-      <c r="I169" s="24"/>
-      <c r="J169" s="24"/>
-      <c r="K169" s="24"/>
-      <c r="L169" s="24"/>
-      <c r="M169" s="24"/>
-      <c r="N169" s="24"/>
-      <c r="O169" s="24"/>
-      <c r="P169" s="24"/>
-      <c r="Q169" s="24"/>
-      <c r="R169" s="24"/>
-      <c r="S169" s="24"/>
-      <c r="T169" s="24"/>
-      <c r="U169" s="24"/>
-      <c r="V169" s="24"/>
-      <c r="W169" s="24"/>
-      <c r="X169" s="24"/>
-      <c r="Y169" s="24"/>
-      <c r="Z169" s="24"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A157:X157"/>
+  <mergeCells count="15">
+    <mergeCell ref="A156:X156"/>
+    <mergeCell ref="F148:H148"/>
+    <mergeCell ref="F149:H149"/>
+    <mergeCell ref="J147:W147"/>
     <mergeCell ref="A1:X1"/>
+    <mergeCell ref="J151:W151"/>
+    <mergeCell ref="F147:H147"/>
+    <mergeCell ref="J146:W146"/>
+    <mergeCell ref="J145:W145"/>
+    <mergeCell ref="F151:H151"/>
+    <mergeCell ref="J149:W149"/>
+    <mergeCell ref="F150:H150"/>
+    <mergeCell ref="J148:W148"/>
+    <mergeCell ref="F146:H146"/>
+    <mergeCell ref="J150:W150"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9669,7 +9845,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -9697,30 +9873,30 @@
     </row>
     <row r="2" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="113" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="102"/>
-      <c r="D2" s="102"/>
-      <c r="E2" s="102"/>
-      <c r="F2" s="102"/>
-      <c r="G2" s="102"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="74"/>
+      <c r="B2" s="139" t="s">
+        <v>299</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="86"/>
     </row>
     <row r="3" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
-      <c r="B3" s="106" t="s">
-        <v>297</v>
-      </c>
-      <c r="C3" s="102"/>
-      <c r="D3" s="102"/>
-      <c r="E3" s="102"/>
-      <c r="F3" s="102"/>
-      <c r="G3" s="102"/>
-      <c r="H3" s="102"/>
-      <c r="I3" s="102"/>
+      <c r="B3" s="122" t="s">
+        <v>300</v>
+      </c>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
       <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -9736,42 +9912,42 @@
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="75"/>
-      <c r="B5" s="112" t="s">
-        <v>298</v>
-      </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="75"/>
+      <c r="A5" s="87"/>
+      <c r="B5" s="140" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="87"/>
     </row>
     <row r="6" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="31"/>
       <c r="B7" s="31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D7" s="31" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E7" s="31" t="s">
         <v>64</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="H7" s="31" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="I7" s="31" t="s">
         <v>82</v>
@@ -9780,368 +9956,610 @@
     </row>
     <row r="8" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
-      <c r="B8" s="76">
+      <c r="B8" s="88">
         <v>1</v>
       </c>
-      <c r="C8" s="77" t="s">
-        <v>305</v>
-      </c>
-      <c r="D8" s="78" t="s">
-        <v>306</v>
-      </c>
-      <c r="E8" s="79" t="s">
+      <c r="C8" s="89" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F8" s="80">
-        <f>BOQ_Matrix!J158</f>
+      <c r="F8" s="92">
+        <f>BOQ_Matrix!J157</f>
         <v>17.319444444444443</v>
       </c>
-      <c r="G8" s="81">
+      <c r="G8" s="93">
         <v>2.88</v>
       </c>
-      <c r="H8" s="82">
+      <c r="H8" s="94">
         <f t="shared" ref="H8:H15" si="0">IFERROR(CEILING(F8/G8,1),"")</f>
         <v>7</v>
       </c>
-      <c r="I8" s="83"/>
+      <c r="I8" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J8" s="9"/>
     </row>
     <row r="9" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
-      <c r="B9" s="84">
+      <c r="B9" s="96">
         <v>2</v>
       </c>
-      <c r="C9" s="85" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="86" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" s="87" t="s">
+      <c r="C9" s="97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D9" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F9" s="88">
-        <f>BOQ_Matrix!K158</f>
+      <c r="F9" s="100">
+        <f>BOQ_Matrix!K157</f>
         <v>155.19631944444444</v>
       </c>
-      <c r="G9" s="89">
+      <c r="G9" s="101">
         <v>2.88</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="102">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="I9" s="91"/>
+      <c r="I9" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10"/>
-      <c r="B10" s="76">
+      <c r="B10" s="88">
         <v>3</v>
       </c>
-      <c r="C10" s="77" t="s">
-        <v>309</v>
-      </c>
-      <c r="D10" s="78" t="s">
-        <v>310</v>
-      </c>
-      <c r="E10" s="79" t="s">
+      <c r="C10" s="89" t="s">
+        <v>313</v>
+      </c>
+      <c r="D10" s="90" t="s">
+        <v>314</v>
+      </c>
+      <c r="E10" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="80">
-        <f>BOQ_Matrix!L158</f>
+      <c r="F10" s="92">
+        <f>BOQ_Matrix!L157</f>
         <v>32.230277777777779</v>
       </c>
-      <c r="G10" s="81">
+      <c r="G10" s="93">
         <v>2.88</v>
       </c>
-      <c r="H10" s="82">
+      <c r="H10" s="94">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="I10" s="83"/>
+      <c r="I10" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J10" s="9"/>
     </row>
     <row r="11" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10"/>
-      <c r="B11" s="84">
+      <c r="B11" s="96">
         <v>4</v>
       </c>
-      <c r="C11" s="85" t="s">
-        <v>311</v>
-      </c>
-      <c r="D11" s="86" t="s">
-        <v>312</v>
-      </c>
-      <c r="E11" s="87" t="s">
+      <c r="C11" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="98" t="s">
+        <v>316</v>
+      </c>
+      <c r="E11" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="88">
-        <f>BOQ_Matrix!M158</f>
+      <c r="F11" s="100">
+        <f>BOQ_Matrix!M157</f>
         <v>685.08069444444459</v>
       </c>
-      <c r="G11" s="89">
+      <c r="G11" s="101">
         <v>2.88</v>
       </c>
-      <c r="H11" s="90">
+      <c r="H11" s="102">
         <f t="shared" si="0"/>
         <v>238</v>
       </c>
-      <c r="I11" s="91"/>
+      <c r="I11" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J11" s="12"/>
     </row>
     <row r="12" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10"/>
-      <c r="B12" s="76">
+      <c r="B12" s="88">
         <v>5</v>
       </c>
-      <c r="C12" s="77" t="s">
-        <v>313</v>
-      </c>
-      <c r="D12" s="78" t="s">
-        <v>314</v>
-      </c>
-      <c r="E12" s="79" t="s">
+      <c r="C12" s="89" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>318</v>
+      </c>
+      <c r="E12" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="80">
-        <f>BOQ_Matrix!N158</f>
+      <c r="F12" s="92">
+        <f>BOQ_Matrix!N157</f>
         <v>155.19631944444444</v>
       </c>
-      <c r="G12" s="81">
+      <c r="G12" s="93">
         <v>2.88</v>
       </c>
-      <c r="H12" s="82">
+      <c r="H12" s="94">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="I12" s="83"/>
+      <c r="I12" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="10"/>
-      <c r="B13" s="84">
+      <c r="B13" s="96">
         <v>6</v>
       </c>
-      <c r="C13" s="85" t="s">
-        <v>315</v>
-      </c>
-      <c r="D13" s="86" t="s">
+      <c r="C13" s="97" t="s">
+        <v>319</v>
+      </c>
+      <c r="D13" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="E13" s="87" t="s">
+      <c r="E13" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="88">
-        <f>BOQ_Matrix!O158</f>
+      <c r="F13" s="100">
+        <f>BOQ_Matrix!O157</f>
         <v>46.331527777777772</v>
       </c>
-      <c r="G13" s="89">
+      <c r="G13" s="101">
         <v>2.88</v>
       </c>
-      <c r="H13" s="90">
+      <c r="H13" s="102">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="I13" s="91"/>
+      <c r="I13" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J13" s="12"/>
     </row>
     <row r="14" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="10"/>
-      <c r="B14" s="76">
+      <c r="B14" s="88">
         <v>7</v>
       </c>
-      <c r="C14" s="77" t="s">
-        <v>316</v>
-      </c>
-      <c r="D14" s="78" t="s">
+      <c r="C14" s="89" t="s">
+        <v>320</v>
+      </c>
+      <c r="D14" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="E14" s="79" t="s">
+      <c r="E14" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F14" s="80">
-        <f>BOQ_Matrix!P158</f>
+      <c r="F14" s="92">
+        <f>BOQ_Matrix!P157</f>
         <v>54.375</v>
       </c>
-      <c r="G14" s="81">
+      <c r="G14" s="93">
         <v>2.88</v>
       </c>
-      <c r="H14" s="82">
+      <c r="H14" s="94">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="I14" s="83"/>
+      <c r="I14" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10"/>
-      <c r="B15" s="84">
+      <c r="B15" s="96">
         <v>8</v>
       </c>
-      <c r="C15" s="85" t="s">
-        <v>317</v>
-      </c>
-      <c r="D15" s="86" t="s">
-        <v>318</v>
-      </c>
-      <c r="E15" s="87" t="s">
+      <c r="C15" s="97" t="s">
+        <v>321</v>
+      </c>
+      <c r="D15" s="98" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F15" s="88">
-        <f>BOQ_Matrix!Q158</f>
-        <v>0</v>
-      </c>
-      <c r="G15" s="89">
+      <c r="F15" s="100">
+        <f>BOQ_Matrix!Q157</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="101">
         <v>2.88</v>
       </c>
-      <c r="H15" s="90">
+      <c r="H15" s="102">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I15" s="91"/>
+      <c r="I15" s="103" t="s">
+        <v>323</v>
+      </c>
       <c r="J15" s="12"/>
     </row>
     <row r="16" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="10"/>
-      <c r="B16" s="76">
+      <c r="B16" s="88">
         <v>9</v>
       </c>
-      <c r="C16" s="77" t="s">
-        <v>319</v>
-      </c>
-      <c r="D16" s="78" t="s">
-        <v>320</v>
-      </c>
-      <c r="E16" s="79" t="s">
-        <v>321</v>
-      </c>
-      <c r="F16" s="80">
-        <f>BOQ_Matrix!R158</f>
-        <v>0</v>
-      </c>
-      <c r="G16" s="92" t="s">
+      <c r="C16" s="89" t="s">
+        <v>324</v>
+      </c>
+      <c r="D16" s="90" t="s">
+        <v>325</v>
+      </c>
+      <c r="E16" s="91" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" s="92">
+        <f>BOQ_Matrix!R157</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="H16" s="92" t="s">
+      <c r="H16" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="I16" s="83"/>
+      <c r="I16" s="95" t="s">
+        <v>327</v>
+      </c>
       <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="10"/>
-      <c r="B17" s="84">
+      <c r="B17" s="96">
         <v>10</v>
       </c>
-      <c r="C17" s="85" t="s">
-        <v>322</v>
-      </c>
-      <c r="D17" s="86" t="s">
-        <v>323</v>
-      </c>
-      <c r="E17" s="87" t="s">
-        <v>321</v>
-      </c>
-      <c r="F17" s="88">
-        <f>BOQ_Matrix!S158</f>
-        <v>0</v>
-      </c>
-      <c r="G17" s="93" t="s">
+      <c r="C17" s="97" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="98" t="s">
+        <v>329</v>
+      </c>
+      <c r="E17" s="99" t="s">
+        <v>326</v>
+      </c>
+      <c r="F17" s="100">
+        <f>BOQ_Matrix!S157</f>
+        <v>0</v>
+      </c>
+      <c r="G17" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="H17" s="93" t="s">
+      <c r="H17" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="I17" s="91"/>
+      <c r="I17" s="103" t="s">
+        <v>330</v>
+      </c>
       <c r="J17" s="12"/>
     </row>
     <row r="18" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
-      <c r="B18" s="76">
+      <c r="B18" s="88">
         <v>11</v>
       </c>
-      <c r="C18" s="77" t="s">
-        <v>324</v>
-      </c>
-      <c r="D18" s="78" t="s">
+      <c r="C18" s="89" t="s">
+        <v>331</v>
+      </c>
+      <c r="D18" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="E18" s="79" t="s">
+      <c r="E18" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="F18" s="80">
-        <f>BOQ_Matrix!T158</f>
-        <v>0</v>
-      </c>
-      <c r="G18" s="92" t="s">
+      <c r="F18" s="92">
+        <f>BOQ_Matrix!T157</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="H18" s="92" t="s">
+      <c r="H18" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="I18" s="83"/>
+      <c r="I18" s="95" t="s">
+        <v>332</v>
+      </c>
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
-      <c r="B19" s="84">
+      <c r="B19" s="96">
         <v>12</v>
       </c>
-      <c r="C19" s="85" t="s">
-        <v>325</v>
-      </c>
-      <c r="D19" s="86" t="s">
+      <c r="C19" s="97" t="s">
+        <v>333</v>
+      </c>
+      <c r="D19" s="98" t="s">
         <v>81</v>
       </c>
-      <c r="E19" s="87" t="s">
+      <c r="E19" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="F19" s="88">
-        <f>BOQ_Matrix!U158</f>
-        <v>0</v>
-      </c>
-      <c r="G19" s="93" t="s">
+      <c r="F19" s="100">
+        <f>BOQ_Matrix!U157</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="H19" s="93" t="s">
+      <c r="H19" s="105" t="s">
         <v>102</v>
       </c>
-      <c r="I19" s="91"/>
+      <c r="I19" s="103" t="s">
+        <v>332</v>
+      </c>
       <c r="J19" s="12"/>
     </row>
-    <row r="20" spans="1:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="74"/>
-      <c r="B21" s="107" t="s">
-        <v>326</v>
-      </c>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="102"/>
-      <c r="I21" s="102"/>
-      <c r="J21" s="74"/>
+    <row r="20" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13"/>
+      <c r="B21" s="138" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="127"/>
+      <c r="D21" s="127"/>
+      <c r="E21" s="127"/>
+      <c r="F21" s="127"/>
+      <c r="G21" s="127"/>
+      <c r="H21" s="127"/>
+      <c r="I21" s="127"/>
+      <c r="J21" s="68"/>
+    </row>
+    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="67"/>
+      <c r="B22" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="C22" s="67" t="s">
+        <v>335</v>
+      </c>
+      <c r="D22" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F22" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="G22" s="67" t="s">
+        <v>277</v>
+      </c>
+      <c r="H22" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="67" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="67"/>
+    </row>
+    <row r="23" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="96">
+        <v>1</v>
+      </c>
+      <c r="C23" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="D23" s="98" t="s">
+        <v>280</v>
+      </c>
+      <c r="E23" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F23" s="106">
+        <v>1</v>
+      </c>
+      <c r="G23" s="107">
+        <f>F23*BOQ_Matrix!H2</f>
+        <v>58</v>
+      </c>
+      <c r="H23" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="103" t="s">
+        <v>282</v>
+      </c>
+      <c r="J23" s="12"/>
+    </row>
+    <row r="24" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="7"/>
+      <c r="B24" s="88">
+        <v>2</v>
+      </c>
+      <c r="C24" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="D24" s="90" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F24" s="108">
+        <v>1</v>
+      </c>
+      <c r="G24" s="109">
+        <f>F24*BOQ_Matrix!H2</f>
+        <v>58</v>
+      </c>
+      <c r="H24" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="95" t="s">
+        <v>285</v>
+      </c>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="96">
+        <v>3</v>
+      </c>
+      <c r="C25" s="97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" s="98" t="s">
+        <v>287</v>
+      </c>
+      <c r="E25" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F25" s="106">
+        <v>1</v>
+      </c>
+      <c r="G25" s="107">
+        <f>F25*BOQ_Matrix!H2</f>
+        <v>58</v>
+      </c>
+      <c r="H25" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="J25" s="12"/>
+    </row>
+    <row r="26" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="7"/>
+      <c r="B26" s="88">
+        <v>4</v>
+      </c>
+      <c r="C26" s="89" t="s">
+        <v>289</v>
+      </c>
+      <c r="D26" s="90" t="s">
+        <v>290</v>
+      </c>
+      <c r="E26" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F26" s="108">
+        <v>1</v>
+      </c>
+      <c r="G26" s="109">
+        <f>F26*BOQ_Matrix!H2</f>
+        <v>58</v>
+      </c>
+      <c r="H26" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="96">
+        <v>5</v>
+      </c>
+      <c r="C27" s="97" t="s">
+        <v>292</v>
+      </c>
+      <c r="D27" s="98" t="s">
+        <v>293</v>
+      </c>
+      <c r="E27" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" s="106">
+        <v>1</v>
+      </c>
+      <c r="G27" s="107">
+        <f>F27*BOQ_Matrix!H2</f>
+        <v>58</v>
+      </c>
+      <c r="H27" s="105" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="103" t="s">
+        <v>294</v>
+      </c>
+      <c r="J27" s="12"/>
+    </row>
+    <row r="28" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="7"/>
+      <c r="B28" s="88">
+        <v>6</v>
+      </c>
+      <c r="C28" s="89" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>296</v>
+      </c>
+      <c r="E28" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="108">
+        <v>15</v>
+      </c>
+      <c r="G28" s="109">
+        <f>F28*BOQ_Matrix!H2</f>
+        <v>870</v>
+      </c>
+      <c r="H28" s="104" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="95" t="s">
+        <v>297</v>
+      </c>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="86"/>
+      <c r="B30" s="123" t="s">
+        <v>336</v>
+      </c>
+      <c r="C30" s="118"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="118"/>
+      <c r="G30" s="118"/>
+      <c r="H30" s="118"/>
+      <c r="I30" s="118"/>
+      <c r="J30" s="86"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10149,16 +10567,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="34" customWidth="1"/>
+    <col min="4" max="4" width="35.109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="4" customWidth="1"/>
   </cols>
@@ -10195,30 +10614,30 @@
     </row>
     <row r="11" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="113" t="s">
-        <v>327</v>
-      </c>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="102"/>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
-      <c r="I11" s="102"/>
-      <c r="J11" s="74"/>
+      <c r="B11" s="139" t="s">
+        <v>337</v>
+      </c>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="86"/>
     </row>
     <row r="12" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="106" t="s">
-        <v>328</v>
-      </c>
-      <c r="C12" s="102"/>
-      <c r="D12" s="102"/>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
-      <c r="I12" s="102"/>
+      <c r="B12" s="122" t="s">
+        <v>338</v>
+      </c>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
       <c r="J12" s="4"/>
     </row>
     <row r="13" spans="1:10" ht="4.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -10252,465 +10671,737 @@
       <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="75"/>
-      <c r="B23" s="112" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" s="102"/>
-      <c r="D23" s="102"/>
-      <c r="E23" s="102"/>
-      <c r="F23" s="102"/>
-      <c r="G23" s="102"/>
-      <c r="H23" s="102"/>
-      <c r="I23" s="102"/>
-      <c r="J23" s="75"/>
+      <c r="A23" s="87"/>
+      <c r="B23" s="140" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="87"/>
     </row>
     <row r="24" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="25" spans="1:10" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="31"/>
       <c r="B25" s="31" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C25" s="31" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D25" s="31" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>64</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="G25" s="31" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="H25" s="31" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="J25" s="31"/>
     </row>
     <row r="26" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="7"/>
-      <c r="B26" s="76">
+      <c r="B26" s="88">
         <v>1</v>
       </c>
-      <c r="C26" s="77" t="s">
-        <v>305</v>
-      </c>
-      <c r="D26" s="78" t="s">
-        <v>306</v>
-      </c>
-      <c r="E26" s="79" t="s">
+      <c r="C26" s="89" t="s">
+        <v>308</v>
+      </c>
+      <c r="D26" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E26" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="80">
+      <c r="F26" s="92">
         <f>Materials_List!F9</f>
         <v>155.19631944444444</v>
       </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="95">
+      <c r="G26" s="110">
+        <v>38.5</v>
+      </c>
+      <c r="H26" s="111">
         <f t="shared" ref="H26:H37" si="0">IFERROR(F26*G26,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I26" s="83"/>
+        <v>5975.0582986111112</v>
+      </c>
+      <c r="I26" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J26" s="9"/>
     </row>
     <row r="27" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
-      <c r="B27" s="84">
+      <c r="B27" s="96">
         <v>2</v>
       </c>
-      <c r="C27" s="85" t="s">
-        <v>307</v>
-      </c>
-      <c r="D27" s="86" t="s">
-        <v>308</v>
-      </c>
-      <c r="E27" s="87" t="s">
+      <c r="C27" s="97" t="s">
+        <v>311</v>
+      </c>
+      <c r="D27" s="98" t="s">
+        <v>312</v>
+      </c>
+      <c r="E27" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F27" s="88">
+      <c r="F27" s="100">
         <f>Materials_List!F10</f>
         <v>32.230277777777779</v>
       </c>
-      <c r="G27" s="94"/>
-      <c r="H27" s="96">
+      <c r="G27" s="110">
+        <v>45</v>
+      </c>
+      <c r="H27" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="91"/>
+        <v>1450.3625</v>
+      </c>
+      <c r="I27" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="7"/>
-      <c r="B28" s="76">
+      <c r="B28" s="88">
         <v>3</v>
       </c>
-      <c r="C28" s="77" t="s">
-        <v>309</v>
-      </c>
-      <c r="D28" s="78" t="s">
-        <v>310</v>
-      </c>
-      <c r="E28" s="79" t="s">
+      <c r="C28" s="89" t="s">
+        <v>313</v>
+      </c>
+      <c r="D28" s="90" t="s">
+        <v>314</v>
+      </c>
+      <c r="E28" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F28" s="80">
+      <c r="F28" s="92">
         <f>Materials_List!F11</f>
         <v>685.08069444444459</v>
       </c>
-      <c r="G28" s="94"/>
-      <c r="H28" s="95">
+      <c r="G28" s="110">
+        <v>52</v>
+      </c>
+      <c r="H28" s="111">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="83"/>
+        <v>35624.196111111116</v>
+      </c>
+      <c r="I28" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
-      <c r="B29" s="84">
+      <c r="B29" s="96">
         <v>4</v>
       </c>
-      <c r="C29" s="85" t="s">
-        <v>311</v>
-      </c>
-      <c r="D29" s="86" t="s">
-        <v>312</v>
-      </c>
-      <c r="E29" s="87" t="s">
+      <c r="C29" s="97" t="s">
+        <v>315</v>
+      </c>
+      <c r="D29" s="98" t="s">
+        <v>316</v>
+      </c>
+      <c r="E29" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F29" s="88">
+      <c r="F29" s="100">
         <f>Materials_List!F12</f>
         <v>155.19631944444444</v>
       </c>
-      <c r="G29" s="94"/>
-      <c r="H29" s="96">
+      <c r="G29" s="110">
+        <v>62</v>
+      </c>
+      <c r="H29" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="91"/>
+        <v>9622.1718055555557</v>
+      </c>
+      <c r="I29" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="7"/>
-      <c r="B30" s="76">
+      <c r="B30" s="88">
         <v>5</v>
       </c>
-      <c r="C30" s="77" t="s">
-        <v>313</v>
-      </c>
-      <c r="D30" s="78" t="s">
-        <v>314</v>
-      </c>
-      <c r="E30" s="79" t="s">
+      <c r="C30" s="89" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" s="90" t="s">
+        <v>318</v>
+      </c>
+      <c r="E30" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F30" s="80">
+      <c r="F30" s="92">
         <f>Materials_List!F13</f>
         <v>46.331527777777772</v>
       </c>
-      <c r="G30" s="94"/>
-      <c r="H30" s="95">
+      <c r="G30" s="110">
+        <v>55</v>
+      </c>
+      <c r="H30" s="111">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I30" s="83"/>
+        <v>2548.2340277777776</v>
+      </c>
+      <c r="I30" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
-      <c r="B31" s="84">
+      <c r="B31" s="96">
         <v>6</v>
       </c>
-      <c r="C31" s="85" t="s">
-        <v>315</v>
-      </c>
-      <c r="D31" s="86" t="s">
+      <c r="C31" s="97" t="s">
+        <v>319</v>
+      </c>
+      <c r="D31" s="98" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="87" t="s">
+      <c r="E31" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F31" s="88">
+      <c r="F31" s="100">
         <f>Materials_List!F14</f>
         <v>54.375</v>
       </c>
-      <c r="G31" s="94"/>
-      <c r="H31" s="96">
+      <c r="G31" s="110">
+        <v>72</v>
+      </c>
+      <c r="H31" s="112">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="91"/>
+        <v>3915</v>
+      </c>
+      <c r="I31" s="103" t="s">
+        <v>310</v>
+      </c>
       <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
-      <c r="B32" s="76">
+      <c r="B32" s="88">
         <v>7</v>
       </c>
-      <c r="C32" s="77" t="s">
-        <v>316</v>
-      </c>
-      <c r="D32" s="78" t="s">
+      <c r="C32" s="89" t="s">
+        <v>320</v>
+      </c>
+      <c r="D32" s="90" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="79" t="s">
+      <c r="E32" s="91" t="s">
         <v>86</v>
       </c>
-      <c r="F32" s="80">
+      <c r="F32" s="92">
         <f>Materials_List!F15</f>
         <v>0</v>
       </c>
-      <c r="G32" s="94"/>
-      <c r="H32" s="95">
+      <c r="G32" s="110">
+        <v>78</v>
+      </c>
+      <c r="H32" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I32" s="83"/>
+      <c r="I32" s="95" t="s">
+        <v>310</v>
+      </c>
       <c r="J32" s="9"/>
     </row>
     <row r="33" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
-      <c r="B33" s="84">
+      <c r="B33" s="96">
         <v>8</v>
       </c>
-      <c r="C33" s="85" t="s">
-        <v>317</v>
-      </c>
-      <c r="D33" s="86" t="s">
-        <v>318</v>
-      </c>
-      <c r="E33" s="87" t="s">
+      <c r="C33" s="97" t="s">
+        <v>321</v>
+      </c>
+      <c r="D33" s="98" t="s">
+        <v>322</v>
+      </c>
+      <c r="E33" s="99" t="s">
         <v>86</v>
       </c>
-      <c r="F33" s="88">
+      <c r="F33" s="100">
         <f>Materials_List!F16</f>
         <v>0</v>
       </c>
-      <c r="G33" s="94"/>
-      <c r="H33" s="96">
+      <c r="G33" s="110">
+        <v>95</v>
+      </c>
+      <c r="H33" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I33" s="91"/>
+      <c r="I33" s="103" t="s">
+        <v>323</v>
+      </c>
       <c r="J33" s="12"/>
     </row>
     <row r="34" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="7"/>
-      <c r="B34" s="76">
+      <c r="B34" s="88">
         <v>9</v>
       </c>
-      <c r="C34" s="77" t="s">
-        <v>319</v>
-      </c>
-      <c r="D34" s="78" t="s">
-        <v>320</v>
-      </c>
-      <c r="E34" s="79" t="s">
-        <v>321</v>
-      </c>
-      <c r="F34" s="80">
+      <c r="C34" s="89" t="s">
+        <v>324</v>
+      </c>
+      <c r="D34" s="90" t="s">
+        <v>325</v>
+      </c>
+      <c r="E34" s="91" t="s">
+        <v>326</v>
+      </c>
+      <c r="F34" s="92">
         <f>Materials_List!F17</f>
         <v>0</v>
       </c>
-      <c r="G34" s="94"/>
-      <c r="H34" s="95">
+      <c r="G34" s="110">
+        <v>18.5</v>
+      </c>
+      <c r="H34" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I34" s="83"/>
+      <c r="I34" s="95" t="s">
+        <v>327</v>
+      </c>
       <c r="J34" s="9"/>
     </row>
     <row r="35" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
-      <c r="B35" s="84">
+      <c r="B35" s="96">
         <v>10</v>
       </c>
-      <c r="C35" s="85" t="s">
-        <v>322</v>
-      </c>
-      <c r="D35" s="86" t="s">
-        <v>323</v>
-      </c>
-      <c r="E35" s="87" t="s">
-        <v>321</v>
-      </c>
-      <c r="F35" s="88">
+      <c r="C35" s="97" t="s">
+        <v>328</v>
+      </c>
+      <c r="D35" s="98" t="s">
+        <v>329</v>
+      </c>
+      <c r="E35" s="99" t="s">
+        <v>326</v>
+      </c>
+      <c r="F35" s="100">
         <f>Materials_List!F18</f>
         <v>0</v>
       </c>
-      <c r="G35" s="94"/>
-      <c r="H35" s="96">
+      <c r="G35" s="110">
+        <v>65</v>
+      </c>
+      <c r="H35" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I35" s="91"/>
+      <c r="I35" s="103" t="s">
+        <v>330</v>
+      </c>
       <c r="J35" s="12"/>
     </row>
     <row r="36" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="7"/>
-      <c r="B36" s="76">
+      <c r="B36" s="88">
         <v>11</v>
       </c>
-      <c r="C36" s="77" t="s">
-        <v>324</v>
-      </c>
-      <c r="D36" s="78" t="s">
+      <c r="C36" s="89" t="s">
+        <v>331</v>
+      </c>
+      <c r="D36" s="90" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="79" t="s">
+      <c r="E36" s="91" t="s">
         <v>99</v>
       </c>
-      <c r="F36" s="80">
+      <c r="F36" s="92">
         <f>Materials_List!F19</f>
         <v>0</v>
       </c>
-      <c r="G36" s="94"/>
-      <c r="H36" s="95">
+      <c r="G36" s="110">
+        <v>12</v>
+      </c>
+      <c r="H36" s="111">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I36" s="83"/>
+      <c r="I36" s="95" t="s">
+        <v>332</v>
+      </c>
       <c r="J36" s="9"/>
     </row>
     <row r="37" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
-      <c r="B37" s="84">
+      <c r="B37" s="96">
         <v>12</v>
       </c>
-      <c r="C37" s="85" t="s">
-        <v>325</v>
-      </c>
-      <c r="D37" s="86" t="s">
+      <c r="C37" s="97" t="s">
+        <v>333</v>
+      </c>
+      <c r="D37" s="98" t="s">
         <v>81</v>
       </c>
-      <c r="E37" s="87" t="s">
+      <c r="E37" s="99" t="s">
         <v>99</v>
       </c>
-      <c r="F37" s="88">
+      <c r="F37" s="100">
         <f>Materials_List!F20</f>
         <v>0</v>
       </c>
-      <c r="G37" s="94"/>
-      <c r="H37" s="96">
+      <c r="G37" s="110">
+        <v>9.5</v>
+      </c>
+      <c r="H37" s="112">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="I37" s="91"/>
+      <c r="I37" s="103" t="s">
+        <v>332</v>
+      </c>
       <c r="J37" s="12"/>
     </row>
     <row r="38" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="97"/>
-      <c r="C39" s="115" t="s">
-        <v>334</v>
-      </c>
-      <c r="D39" s="102"/>
-      <c r="E39" s="102"/>
-      <c r="F39" s="102"/>
-      <c r="G39" s="102"/>
-      <c r="H39" s="98">
-        <f>SUM(H26:H37)</f>
-        <v>0</v>
-      </c>
-      <c r="I39" s="97"/>
-      <c r="J39" s="97"/>
-    </row>
-    <row r="40" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="116" t="s">
+    <row r="39" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="138" t="s">
+        <v>344</v>
+      </c>
+      <c r="C39" s="127"/>
+      <c r="D39" s="127"/>
+      <c r="E39" s="127"/>
+      <c r="F39" s="127"/>
+      <c r="G39" s="127"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="127"/>
+      <c r="J39" s="68"/>
+    </row>
+    <row r="40" spans="1:10" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="67"/>
+      <c r="B40" s="67" t="s">
+        <v>302</v>
+      </c>
+      <c r="C40" s="67" t="s">
         <v>335</v>
       </c>
-      <c r="D40" s="102"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="102"/>
-      <c r="H40" s="99">
-        <f>H39*0.05</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-    </row>
-    <row r="41" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="74"/>
-      <c r="C41" s="114" t="s">
-        <v>336</v>
-      </c>
-      <c r="D41" s="102"/>
-      <c r="E41" s="102"/>
-      <c r="F41" s="102"/>
-      <c r="G41" s="102"/>
-      <c r="H41" s="100">
-        <f>H39+H40</f>
-        <v>0</v>
-      </c>
-      <c r="I41" s="74"/>
-      <c r="J41" s="74"/>
-    </row>
-    <row r="42" spans="1:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C44" s="1"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="D45" s="1"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="E46" s="1"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F47" s="1"/>
-    </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="G48" s="1"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="I50" s="1"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="74"/>
-      <c r="B52" s="107" t="s">
-        <v>337</v>
-      </c>
-      <c r="C52" s="102"/>
-      <c r="D52" s="102"/>
-      <c r="E52" s="102"/>
-      <c r="F52" s="102"/>
-      <c r="G52" s="102"/>
-      <c r="H52" s="102"/>
-      <c r="I52" s="102"/>
-      <c r="J52" s="74"/>
+      <c r="D40" s="67" t="s">
+        <v>30</v>
+      </c>
+      <c r="E40" s="67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F40" s="67" t="s">
+        <v>340</v>
+      </c>
+      <c r="G40" s="67" t="s">
+        <v>341</v>
+      </c>
+      <c r="H40" s="67" t="s">
+        <v>342</v>
+      </c>
+      <c r="I40" s="67" t="s">
+        <v>343</v>
+      </c>
+      <c r="J40" s="67"/>
+    </row>
+    <row r="41" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="10"/>
+      <c r="B41" s="96">
+        <v>1</v>
+      </c>
+      <c r="C41" s="97" t="s">
+        <v>279</v>
+      </c>
+      <c r="D41" s="98" t="s">
+        <v>280</v>
+      </c>
+      <c r="E41" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F41" s="107">
+        <f>Materials_List!G24</f>
+        <v>58</v>
+      </c>
+      <c r="G41" s="110">
+        <v>850</v>
+      </c>
+      <c r="H41" s="112">
+        <f t="shared" ref="H41:H46" si="1">IFERROR(F41*G41,"")</f>
+        <v>49300</v>
+      </c>
+      <c r="I41" s="103" t="s">
+        <v>282</v>
+      </c>
+      <c r="J41" s="12"/>
+    </row>
+    <row r="42" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="7"/>
+      <c r="B42" s="88">
+        <v>2</v>
+      </c>
+      <c r="C42" s="89" t="s">
+        <v>283</v>
+      </c>
+      <c r="D42" s="90" t="s">
+        <v>284</v>
+      </c>
+      <c r="E42" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F42" s="109">
+        <f>Materials_List!G25</f>
+        <v>58</v>
+      </c>
+      <c r="G42" s="110">
+        <v>420</v>
+      </c>
+      <c r="H42" s="111">
+        <f t="shared" si="1"/>
+        <v>24360</v>
+      </c>
+      <c r="I42" s="95" t="s">
+        <v>285</v>
+      </c>
+      <c r="J42" s="9"/>
+    </row>
+    <row r="43" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="10"/>
+      <c r="B43" s="96">
+        <v>3</v>
+      </c>
+      <c r="C43" s="97" t="s">
+        <v>286</v>
+      </c>
+      <c r="D43" s="98" t="s">
+        <v>287</v>
+      </c>
+      <c r="E43" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F43" s="107">
+        <f>Materials_List!G26</f>
+        <v>58</v>
+      </c>
+      <c r="G43" s="110">
+        <v>1200</v>
+      </c>
+      <c r="H43" s="112">
+        <f t="shared" si="1"/>
+        <v>69600</v>
+      </c>
+      <c r="I43" s="103" t="s">
+        <v>288</v>
+      </c>
+      <c r="J43" s="12"/>
+    </row>
+    <row r="44" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="7"/>
+      <c r="B44" s="88">
+        <v>4</v>
+      </c>
+      <c r="C44" s="89" t="s">
+        <v>289</v>
+      </c>
+      <c r="D44" s="90" t="s">
+        <v>290</v>
+      </c>
+      <c r="E44" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F44" s="109">
+        <f>Materials_List!G27</f>
+        <v>58</v>
+      </c>
+      <c r="G44" s="110">
+        <v>2800</v>
+      </c>
+      <c r="H44" s="111">
+        <f t="shared" si="1"/>
+        <v>162400</v>
+      </c>
+      <c r="I44" s="95" t="s">
+        <v>291</v>
+      </c>
+      <c r="J44" s="9"/>
+    </row>
+    <row r="45" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="10"/>
+      <c r="B45" s="96">
+        <v>5</v>
+      </c>
+      <c r="C45" s="97" t="s">
+        <v>292</v>
+      </c>
+      <c r="D45" s="98" t="s">
+        <v>293</v>
+      </c>
+      <c r="E45" s="99" t="s">
+        <v>281</v>
+      </c>
+      <c r="F45" s="107">
+        <f>Materials_List!G28</f>
+        <v>870</v>
+      </c>
+      <c r="G45" s="110">
+        <v>950</v>
+      </c>
+      <c r="H45" s="112">
+        <f t="shared" si="1"/>
+        <v>826500</v>
+      </c>
+      <c r="I45" s="103" t="s">
+        <v>294</v>
+      </c>
+      <c r="J45" s="12"/>
+    </row>
+    <row r="46" spans="1:10" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="88">
+        <v>6</v>
+      </c>
+      <c r="C46" s="89" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="90" t="s">
+        <v>296</v>
+      </c>
+      <c r="E46" s="91" t="s">
+        <v>281</v>
+      </c>
+      <c r="F46" s="109">
+        <f>Materials_List!G29</f>
+        <v>0</v>
+      </c>
+      <c r="G46" s="110">
+        <v>35</v>
+      </c>
+      <c r="H46" s="111">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I46" s="95" t="s">
+        <v>297</v>
+      </c>
+      <c r="J46" s="9"/>
+    </row>
+    <row r="47" spans="1:10" ht="7.95" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="B48" s="113"/>
+      <c r="C48" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="118"/>
+      <c r="G48" s="118"/>
+      <c r="H48" s="114">
+        <f>IFERROR(H26,0)+IFERROR(H27,0)+IFERROR(H28,0)+IFERROR(H29,0)+IFERROR(H30,0)+IFERROR(H31,0)+IFERROR(H32,0)+IFERROR(H33,0)+IFERROR(H34,0)+IFERROR(H35,0)+IFERROR(H36,0)+IFERROR(H37,0)+IFERROR(H41,0)+IFERROR(H42,0)+IFERROR(H43,0)+IFERROR(H44,0)+IFERROR(H45,0)+IFERROR(H46,0)</f>
+        <v>1191295.0227430556</v>
+      </c>
+      <c r="I48" s="113"/>
+      <c r="J48" s="113"/>
+    </row>
+    <row r="49" spans="1:10" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="4"/>
+      <c r="C49" s="141" t="s">
+        <v>346</v>
+      </c>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="G49" s="118"/>
+      <c r="H49" s="115">
+        <f>H48*0.05</f>
+        <v>59564.75113715278</v>
+      </c>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+    </row>
+    <row r="50" spans="1:10" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1"/>
+      <c r="B50" s="86"/>
+      <c r="C50" s="142" t="s">
+        <v>347</v>
+      </c>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="118"/>
+      <c r="G50" s="118"/>
+      <c r="H50" s="116">
+        <f>H48+H49</f>
+        <v>1250859.7738802084</v>
+      </c>
+      <c r="I50" s="86"/>
+      <c r="J50" s="86"/>
+    </row>
+    <row r="51" spans="1:10" ht="4.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B52" s="1"/>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="D54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="G57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J60" s="1"/>
+    </row>
+    <row r="61" spans="1:10" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="86"/>
+      <c r="B61" s="123" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" s="118"/>
+      <c r="D61" s="118"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="118"/>
+      <c r="G61" s="118"/>
+      <c r="H61" s="118"/>
+      <c r="I61" s="118"/>
+      <c r="J61" s="86"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
+    <mergeCell ref="B61:I61"/>
+    <mergeCell ref="B23:I23"/>
+    <mergeCell ref="C48:G48"/>
     <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B52:I52"/>
+    <mergeCell ref="C49:G49"/>
+    <mergeCell ref="B39:I39"/>
     <mergeCell ref="B11:I11"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="B23:I23"/>
-    <mergeCell ref="C39:G39"/>
-    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="C50:G50"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
